--- a/FichiersClaude/comparaison_EBA/Comparaison_EBA_vs_resultats_2025-12-31.xlsx
+++ b/FichiersClaude/comparaison_EBA/Comparaison_EBA_vs_resultats_2025-12-31.xlsx
@@ -3990,23 +3990,17 @@
       <c r="D100" t="n">
         <v>0.2655908389071193</v>
       </c>
-      <c r="E100" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="F100" t="n">
-        <v>-0.0004091610928806944</v>
-      </c>
-      <c r="G100" t="n">
-        <v>-0.1538199597295843</v>
-      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>page 169 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -4029,23 +4023,17 @@
       <c r="D101" t="n">
         <v>0.2655908389071193</v>
       </c>
-      <c r="E101" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="F101" t="n">
-        <v>-0.0004091610928806944</v>
-      </c>
-      <c r="G101" t="n">
-        <v>-0.1538199597295843</v>
-      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>page 169 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -4068,23 +4056,17 @@
       <c r="D102" t="n">
         <v>0.2689824401489651</v>
       </c>
-      <c r="E102" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="F102" t="n">
-        <v>-1.755985103485402e-05</v>
-      </c>
-      <c r="G102" t="n">
-        <v>-0.006527825663514508</v>
-      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>page 169 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -4251,23 +4233,17 @@
       <c r="D107" t="n">
         <v>2430371371.15</v>
       </c>
-      <c r="E107" t="n">
-        <v>2430000000</v>
-      </c>
-      <c r="F107" t="n">
-        <v>371371.1500000954</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0.01528276337448952</v>
-      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>page 169 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -4290,23 +4266,17 @@
       <c r="D108" t="n">
         <v>2461407270.56</v>
       </c>
-      <c r="E108" t="n">
-        <v>2461000000</v>
-      </c>
-      <c r="F108" t="n">
-        <v>407270.5599999428</v>
-      </c>
-      <c r="G108" t="n">
-        <v>0.01654898659081442</v>
-      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>page 169 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -4329,23 +4299,17 @@
       <c r="D109" t="n">
         <v>9150810250.65</v>
       </c>
-      <c r="E109" t="n">
-        <v>9151000000</v>
-      </c>
-      <c r="F109" t="n">
-        <v>-189749.3500003815</v>
-      </c>
-      <c r="G109" t="n">
-        <v>-0.002073536771941662</v>
-      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>page 169 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4348,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>page 169 (table)</t>
+          <t>page 169 (OCR table)</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4451,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>page 169 (table)</t>
+          <t>page 169 (OCR table)</t>
         </is>
       </c>
     </row>
@@ -6889,17 +6853,23 @@
       <c r="D183" t="n">
         <v>910989655</v>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
+      <c r="E183" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F183" t="n">
+        <v>902989655</v>
+      </c>
+      <c r="G183" t="n">
+        <v>11287.3706875</v>
+      </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Non trouvé dans le PDF</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 37</t>
         </is>
       </c>
     </row>
@@ -8335,17 +8305,23 @@
       <c r="D225" t="n">
         <v>894333330</v>
       </c>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
+      <c r="E225" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F225" t="n">
+        <v>886333330</v>
+      </c>
+      <c r="G225" t="n">
+        <v>11079.166625</v>
+      </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Non trouvé dans le PDF</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 37</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9311,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C254" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
@@ -9364,7 +9344,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C255" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
@@ -9393,7 +9377,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C256" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
@@ -9422,7 +9410,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C257" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
@@ -9451,7 +9443,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C258" t="inlineStr">
         <is>
           <t>LCR</t>
@@ -9480,7 +9476,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C259" t="inlineStr">
         <is>
           <t>NSFR</t>
@@ -9509,7 +9509,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C260" t="inlineStr">
         <is>
           <t>CET1 Capital</t>
@@ -9538,7 +9542,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C261" t="inlineStr">
         <is>
           <t>Tier 1 Capital</t>
@@ -9567,7 +9575,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C262" t="inlineStr">
         <is>
           <t>Total Capital</t>
@@ -9596,7 +9608,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C263" t="inlineStr">
         <is>
           <t>RWA Total</t>
@@ -9625,7 +9641,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C264" t="inlineStr">
         <is>
           <t>RWA Crédit</t>
@@ -9654,7 +9674,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C265" t="inlineStr">
         <is>
           <t>RWA CCR</t>
@@ -9683,7 +9707,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C266" t="inlineStr">
         <is>
           <t>RWA Marché</t>
@@ -9712,7 +9740,11 @@
           <t>Caisse fédérale de crédit mutuel</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>969500RIQZX7RZNR4Z50</t>
+        </is>
+      </c>
       <c r="C267" t="inlineStr">
         <is>
           <t>RWA Opérationnel</t>
@@ -10606,10 +10638,14 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C296" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
@@ -10633,10 +10669,14 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C297" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
@@ -10660,10 +10700,14 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C298" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
@@ -10687,10 +10731,14 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C299" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
@@ -10714,10 +10762,14 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C300" t="inlineStr">
         <is>
           <t>LCR</t>
@@ -10741,10 +10793,14 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C301" t="inlineStr">
         <is>
           <t>NSFR</t>
@@ -10768,10 +10824,14 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C302" t="inlineStr">
         <is>
           <t>CET1 Capital</t>
@@ -10795,10 +10855,14 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C303" t="inlineStr">
         <is>
           <t>Tier 1 Capital</t>
@@ -10822,10 +10886,14 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C304" t="inlineStr">
         <is>
           <t>Total Capital</t>
@@ -10849,10 +10917,14 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C305" t="inlineStr">
         <is>
           <t>RWA Total</t>
@@ -10876,10 +10948,14 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C306" t="inlineStr">
         <is>
           <t>RWA Crédit</t>
@@ -10903,10 +10979,14 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C307" t="inlineStr">
         <is>
           <t>RWA CCR</t>
@@ -10930,10 +11010,14 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C308" t="inlineStr">
         <is>
           <t>RWA Marché</t>
@@ -10957,10 +11041,14 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Confédération Nationale du Cré</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr"/>
+          <t>Confédération Nationale du Crédit Mutuel</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>969500DZUEMFZXPMKV94</t>
+        </is>
+      </c>
       <c r="C309" t="inlineStr">
         <is>
           <t>RWA Opérationnel</t>

--- a/FichiersClaude/comparaison_EBA/Comparaison_EBA_vs_resultats_2025-12-31.xlsx
+++ b/FichiersClaude/comparaison_EBA/Comparaison_EBA_vs_resultats_2025-12-31.xlsx
@@ -2129,17 +2129,23 @@
       <c r="D49" t="n">
         <v>1.0701</v>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-102.4299</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-98.96608695652174</v>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Non trouvé dans le PDF</t>
+          <t>ANOMALIE UNITE PROBABLE (facteur ~100, fichier resultats)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 104 (Qwen2.5-VL)</t>
         </is>
       </c>
     </row>
@@ -2394,17 +2400,19 @@
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>37812211</v>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Non trouvé dans le PDF</t>
+          <t>Absent du fichier resultats</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 149 (Qwen2.5-VL)</t>
         </is>
       </c>
     </row>
@@ -3507,17 +3515,23 @@
       <c r="D87" t="n">
         <v>0.1798597690275607</v>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-0.0001402309724393425</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-0.0779060957996347</v>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Non trouvé dans le PDF</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 17 (Qwen2.5-VL)</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4491,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -4508,7 +4522,7 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -4539,7 +4553,7 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -4570,7 +4584,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -4603,7 +4617,7 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -4636,7 +4650,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -4667,7 +4681,7 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -4698,7 +4712,7 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -4729,7 +4743,7 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -4760,7 +4774,7 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -4791,7 +4805,7 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -4822,7 +4836,7 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -4853,7 +4867,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -4884,7 +4898,7 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Groupe BPCE)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5397,7 +5411,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5408,17 +5422,23 @@
       <c r="D142" t="n">
         <v>0.2099646719607195</v>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+      <c r="E142" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.05596467196071947</v>
+      </c>
+      <c r="G142" t="n">
+        <v>36.34069607838926</v>
+      </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 9 (table)</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5450,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5441,17 +5461,23 @@
       <c r="D143" t="n">
         <v>0.2099646719607195</v>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
+      <c r="E143" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.03196467196071945</v>
+      </c>
+      <c r="G143" t="n">
+        <v>17.95768087680868</v>
+      </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 10 (table)</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5489,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5474,17 +5500,23 @@
       <c r="D144" t="n">
         <v>0.2417087285470789</v>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+      <c r="E144" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.03270872854707887</v>
+      </c>
+      <c r="G144" t="n">
+        <v>15.65010935266932</v>
+      </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 10 (table)</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5528,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5507,17 +5539,23 @@
       <c r="D145" t="n">
         <v>0.08173300507627101</v>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+      <c r="E145" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.02873300507627102</v>
+      </c>
+      <c r="G145" t="n">
+        <v>54.21321712503966</v>
+      </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 9 (table)</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5567,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5540,17 +5578,23 @@
       <c r="D146" t="n">
         <v>2.431033333333334</v>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
+      <c r="E146" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.9010333333333336</v>
+      </c>
+      <c r="G146" t="n">
+        <v>58.89106753812637</v>
+      </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 9 (table)</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5606,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5573,17 +5617,23 @@
       <c r="D147" t="n">
         <v>1.2608028</v>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="E147" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F147" t="n">
+        <v>-0.1491971999999999</v>
+      </c>
+      <c r="G147" t="n">
+        <v>-10.58136170212765</v>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 9 (table)</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5645,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5606,17 +5656,23 @@
       <c r="D148" t="n">
         <v>8864214631.894703</v>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
+      <c r="E148" t="n">
+        <v>20900000</v>
+      </c>
+      <c r="F148" t="n">
+        <v>8843314631.894703</v>
+      </c>
+      <c r="G148" t="n">
+        <v>42312.51020045312</v>
+      </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 9 (table)</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5684,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5639,17 +5695,23 @@
       <c r="D149" t="n">
         <v>8864214631.894703</v>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
+      <c r="E149" t="n">
+        <v>24127000000</v>
+      </c>
+      <c r="F149" t="n">
+        <v>-15262785368.1053</v>
+      </c>
+      <c r="G149" t="n">
+        <v>-63.26018720978694</v>
+      </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 10 (table)</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5723,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5672,17 +5734,23 @@
       <c r="D150" t="n">
         <v>10204374041.76505</v>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+      <c r="E150" t="n">
+        <v>28241000000</v>
+      </c>
+      <c r="F150" t="n">
+        <v>-18036625958.23495</v>
+      </c>
+      <c r="G150" t="n">
+        <v>-63.86681051745671</v>
+      </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 10 (table)</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5762,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5705,17 +5773,23 @@
       <c r="D151" t="n">
         <v>42217648088.6891</v>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
+      <c r="E151" t="n">
+        <v>135398000000</v>
+      </c>
+      <c r="F151" t="n">
+        <v>-93180351911.3109</v>
+      </c>
+      <c r="G151" t="n">
+        <v>-68.8195925429555</v>
+      </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 10 (table)</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5801,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5738,17 +5812,23 @@
       <c r="D152" t="n">
         <v>1521669142.132596</v>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
+      <c r="E152" t="n">
+        <v>108376000000</v>
+      </c>
+      <c r="F152" t="n">
+        <v>-106854330857.8674</v>
+      </c>
+      <c r="G152" t="n">
+        <v>-98.59593531581476</v>
+      </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 15 (table)</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5840,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5771,17 +5851,23 @@
       <c r="D153" t="n">
         <v>18300108182.78608</v>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+      <c r="E153" t="n">
+        <v>6902000000</v>
+      </c>
+      <c r="F153" t="n">
+        <v>11398108182.78608</v>
+      </c>
+      <c r="G153" t="n">
+        <v>165.1421063863529</v>
+      </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 15 (table)</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5879,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5804,17 +5890,23 @@
       <c r="D154" t="n">
         <v>657355257.8779061</v>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
+      <c r="E154" t="n">
+        <v>2025000000</v>
+      </c>
+      <c r="F154" t="n">
+        <v>-1367644742.122094</v>
+      </c>
+      <c r="G154" t="n">
+        <v>-67.53801195664661</v>
+      </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 14 (OCR table)</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5918,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>R4DHLH5KX7NMDO6YTPM4</t>
+          <t>BFXS5XCH7N0Y05NIXW11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5837,17 +5929,23 @@
       <c r="D155" t="n">
         <v>14694335353.459</v>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
+      <c r="E155" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="F155" t="n">
+        <v>14676735353.459</v>
+      </c>
+      <c r="G155" t="n">
+        <v>83390.54178101705</v>
+      </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 14 (OCR table)</t>
         </is>
       </c>
     </row>
@@ -6030,14 +6128,14 @@
         <v>4.201000000000001</v>
       </c>
       <c r="F160" t="n">
-        <v>415.8982</v>
+        <v>-0.0008000000000265572</v>
       </c>
       <c r="G160" t="n">
-        <v>9899.980956915018</v>
+        <v>-0.0001904308498039888</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -6069,14 +6167,14 @@
         <v>1.1757</v>
       </c>
       <c r="F161" t="n">
-        <v>116.3943</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>9899.999999999998</v>
+        <v>0</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -6897,7 +6995,7 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -6930,7 +7028,7 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -6963,7 +7061,7 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -6996,7 +7094,7 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -7029,7 +7127,7 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -7062,7 +7160,7 @@
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -7095,7 +7193,7 @@
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -7128,7 +7226,7 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -7161,7 +7259,7 @@
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -7194,7 +7292,7 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -7227,7 +7325,7 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -7260,7 +7358,7 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -7293,7 +7391,7 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -7326,7 +7424,7 @@
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -7393,17 +7491,23 @@
       <c r="D199" t="n">
         <v>0.2453352409342637</v>
       </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
+      <c r="E199" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.0003352409342637086</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.1368330343933505</v>
+      </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Non trouvé dans le PDF</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>auto-extraction (KM1/OV1 regex)</t>
+          <t>page 108 (Qwen2.5-VL)</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9433,7 @@
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -9362,7 +9466,7 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -9395,7 +9499,7 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -9428,7 +9532,7 @@
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -9461,7 +9565,7 @@
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -9494,7 +9598,7 @@
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -9527,7 +9631,7 @@
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -9560,7 +9664,7 @@
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -9593,7 +9697,7 @@
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -9626,7 +9730,7 @@
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -9659,7 +9763,7 @@
       <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -9692,7 +9796,7 @@
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -9725,7 +9829,7 @@
       <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -9758,7 +9862,7 @@
       <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Confédération Nationale du Crédit Mutuel)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -9789,7 +9893,7 @@
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -9820,7 +9924,7 @@
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -9851,7 +9955,7 @@
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -9882,7 +9986,7 @@
       <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -9913,7 +10017,7 @@
       <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -9944,7 +10048,7 @@
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -9975,7 +10079,7 @@
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -10006,7 +10110,7 @@
       <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -10037,7 +10141,7 @@
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -10068,7 +10172,7 @@
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -10099,7 +10203,7 @@
       <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -10130,7 +10234,7 @@
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -10161,7 +10265,7 @@
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -10192,7 +10296,7 @@
       <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -10223,7 +10327,7 @@
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -10254,7 +10358,7 @@
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -10285,7 +10389,7 @@
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -10316,7 +10420,7 @@
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -10347,7 +10451,7 @@
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -10378,7 +10482,7 @@
       <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -10409,7 +10513,7 @@
       <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -10440,7 +10544,7 @@
       <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -10471,7 +10575,7 @@
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -10502,7 +10606,7 @@
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -10533,7 +10637,7 @@
       <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -10564,7 +10668,7 @@
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -10595,7 +10699,7 @@
       <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -10626,7 +10730,7 @@
       <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr">
         <is>
-          <t>PDF non disponible</t>
+          <t>Données consolidées au niveau parent (Crédit Agricole)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -13764,14 +13868,14 @@
         <v>1.4826</v>
       </c>
       <c r="F384" t="n">
-        <v>146.7804</v>
+        <v>0.003000000000014325</v>
       </c>
       <c r="G384" t="n">
-        <v>9900.202347227843</v>
+        <v>0.002023472278439447</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -13803,14 +13907,14 @@
         <v>1.1633</v>
       </c>
       <c r="F385" t="n">
-        <v>115.168</v>
+        <v>0.001300000000000523</v>
       </c>
       <c r="G385" t="n">
-        <v>9900.111751053038</v>
+        <v>0.00111751053038814</v>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">

--- a/FichiersClaude/comparaison_EBA/Comparaison_EBA_vs_resultats_2025-12-31.xlsx
+++ b/FichiersClaude/comparaison_EBA/Comparaison_EBA_vs_resultats_2025-12-31.xlsx
@@ -600,17 +600,17 @@
         <v>0.0512</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0225</v>
+        <v>0.0512</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0287</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>127.5555555555556</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1946,23 +1946,17 @@
       <c r="D44" t="n">
         <v>0.2079427881739253</v>
       </c>
-      <c r="E44" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-5.721182607468234e-05</v>
-      </c>
-      <c r="G44" t="n">
-        <v>-0.02750568561282804</v>
-      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>page 148 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -2129,23 +2123,17 @@
       <c r="D49" t="n">
         <v>1.0701</v>
       </c>
-      <c r="E49" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-102.4299</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-98.96608695652174</v>
-      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ANOMALIE UNITE PROBABLE (facteur ~100, fichier resultats)</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>page 104 (Qwen2.5-VL)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -2400,19 +2388,17 @@
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="n">
-        <v>37812211</v>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Absent du fichier resultats</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>page 149 (Qwen2.5-VL)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -2667,19 +2653,17 @@
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="n">
-        <v>1.0829</v>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Absent du fichier resultats</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>page 8 (OCR table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -2859,13 +2843,13 @@
         <v>566950024783.033</v>
       </c>
       <c r="E68" t="n">
-        <v>420000000</v>
+        <v>595000000</v>
       </c>
       <c r="F68" t="n">
-        <v>566530024783.033</v>
+        <v>566355024783.033</v>
       </c>
       <c r="G68" t="n">
-        <v>134888.1011388174</v>
+        <v>95185.71845092991</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2874,7 +2858,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>page 1 (OCR table)</t>
+          <t>page 2 (OCR table)</t>
         </is>
       </c>
     </row>
@@ -2897,23 +2881,17 @@
       <c r="D69" t="n">
         <v>40175045947.4999</v>
       </c>
-      <c r="E69" t="n">
-        <v>526000000</v>
-      </c>
-      <c r="F69" t="n">
-        <v>39649045947.4999</v>
-      </c>
-      <c r="G69" t="n">
-        <v>7537.841434885912</v>
-      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>page 2 (OCR table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -2976,13 +2954,13 @@
         <v>112475232762.5</v>
       </c>
       <c r="E71" t="n">
-        <v>586000000</v>
+        <v>1000000</v>
       </c>
       <c r="F71" t="n">
-        <v>111889232762.5</v>
+        <v>112474232762.5</v>
       </c>
       <c r="G71" t="n">
-        <v>19093.72572738908</v>
+        <v>11247423.27625</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2991,7 +2969,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>page 2 (OCR table)</t>
+          <t>page 3 (OCR table)</t>
         </is>
       </c>
     </row>
@@ -3177,19 +3155,17 @@
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="n">
-        <v>1.0829</v>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Absent du fichier resultats</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>page 8 (OCR table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3319,7 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>420000000</v>
+        <v>595000000</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
@@ -3354,7 +3330,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>page 1 (OCR table)</t>
+          <t>page 2 (OCR table)</t>
         </is>
       </c>
     </row>
@@ -3375,19 +3351,17 @@
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="n">
-        <v>526000000</v>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Absent du fichier resultats</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>page 2 (OCR table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3416,7 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>586000000</v>
+        <v>1000000</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
@@ -3453,7 +3427,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>page 2 (OCR table)</t>
+          <t>page 3 (OCR table)</t>
         </is>
       </c>
     </row>
@@ -3515,23 +3489,17 @@
       <c r="D87" t="n">
         <v>0.1798597690275607</v>
       </c>
-      <c r="E87" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F87" t="n">
-        <v>-0.0001402309724393425</v>
-      </c>
-      <c r="G87" t="n">
-        <v>-0.0779060957996347</v>
-      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>page 17 (Qwen2.5-VL)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -4136,23 +4104,17 @@
       <c r="D104" t="n">
         <v>1.4499</v>
       </c>
-      <c r="E104" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0.4499</v>
-      </c>
-      <c r="G104" t="n">
-        <v>44.98999999999999</v>
-      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>page 118 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5059,13 +5021,13 @@
         <v>1.3512</v>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>8.52</v>
       </c>
       <c r="F132" t="n">
-        <v>0.3512</v>
+        <v>-7.168799999999999</v>
       </c>
       <c r="G132" t="n">
-        <v>35.12</v>
+        <v>-84.14084507042253</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5074,7 +5036,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>page 100 (table)</t>
+          <t>page 101 (table)</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5373,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5422,23 +5384,17 @@
       <c r="D142" t="n">
         <v>0.2099646719607195</v>
       </c>
-      <c r="E142" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="F142" t="n">
-        <v>0.05596467196071947</v>
-      </c>
-      <c r="G142" t="n">
-        <v>36.34069607838926</v>
-      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>page 9 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5406,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5461,23 +5417,17 @@
       <c r="D143" t="n">
         <v>0.2099646719607195</v>
       </c>
-      <c r="E143" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="F143" t="n">
-        <v>0.03196467196071945</v>
-      </c>
-      <c r="G143" t="n">
-        <v>17.95768087680868</v>
-      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>page 10 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5439,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5500,23 +5450,17 @@
       <c r="D144" t="n">
         <v>0.2417087285470789</v>
       </c>
-      <c r="E144" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0.03270872854707887</v>
-      </c>
-      <c r="G144" t="n">
-        <v>15.65010935266932</v>
-      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>page 10 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5472,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5539,23 +5483,17 @@
       <c r="D145" t="n">
         <v>0.08173300507627101</v>
       </c>
-      <c r="E145" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0.02873300507627102</v>
-      </c>
-      <c r="G145" t="n">
-        <v>54.21321712503966</v>
-      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>page 9 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5505,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5578,23 +5516,17 @@
       <c r="D146" t="n">
         <v>2.431033333333334</v>
       </c>
-      <c r="E146" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="F146" t="n">
-        <v>0.9010333333333336</v>
-      </c>
-      <c r="G146" t="n">
-        <v>58.89106753812637</v>
-      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>page 9 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5538,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5617,23 +5549,17 @@
       <c r="D147" t="n">
         <v>1.2608028</v>
       </c>
-      <c r="E147" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="F147" t="n">
-        <v>-0.1491971999999999</v>
-      </c>
-      <c r="G147" t="n">
-        <v>-10.58136170212765</v>
-      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>page 9 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5571,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5656,23 +5582,17 @@
       <c r="D148" t="n">
         <v>8864214631.894703</v>
       </c>
-      <c r="E148" t="n">
-        <v>20900000</v>
-      </c>
-      <c r="F148" t="n">
-        <v>8843314631.894703</v>
-      </c>
-      <c r="G148" t="n">
-        <v>42312.51020045312</v>
-      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>page 9 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5604,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5695,23 +5615,17 @@
       <c r="D149" t="n">
         <v>8864214631.894703</v>
       </c>
-      <c r="E149" t="n">
-        <v>24127000000</v>
-      </c>
-      <c r="F149" t="n">
-        <v>-15262785368.1053</v>
-      </c>
-      <c r="G149" t="n">
-        <v>-63.26018720978694</v>
-      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>page 10 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5637,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5734,23 +5648,17 @@
       <c r="D150" t="n">
         <v>10204374041.76505</v>
       </c>
-      <c r="E150" t="n">
-        <v>28241000000</v>
-      </c>
-      <c r="F150" t="n">
-        <v>-18036625958.23495</v>
-      </c>
-      <c r="G150" t="n">
-        <v>-63.86681051745671</v>
-      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>page 10 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5670,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5773,23 +5681,17 @@
       <c r="D151" t="n">
         <v>42217648088.6891</v>
       </c>
-      <c r="E151" t="n">
-        <v>135398000000</v>
-      </c>
-      <c r="F151" t="n">
-        <v>-93180351911.3109</v>
-      </c>
-      <c r="G151" t="n">
-        <v>-68.8195925429555</v>
-      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>page 10 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5703,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5812,23 +5714,17 @@
       <c r="D152" t="n">
         <v>1521669142.132596</v>
       </c>
-      <c r="E152" t="n">
-        <v>108376000000</v>
-      </c>
-      <c r="F152" t="n">
-        <v>-106854330857.8674</v>
-      </c>
-      <c r="G152" t="n">
-        <v>-98.59593531581476</v>
-      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>page 15 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5736,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5851,23 +5747,17 @@
       <c r="D153" t="n">
         <v>18300108182.78608</v>
       </c>
-      <c r="E153" t="n">
-        <v>6902000000</v>
-      </c>
-      <c r="F153" t="n">
-        <v>11398108182.78608</v>
-      </c>
-      <c r="G153" t="n">
-        <v>165.1421063863529</v>
-      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>page 15 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5769,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5890,23 +5780,17 @@
       <c r="D154" t="n">
         <v>657355257.8779061</v>
       </c>
-      <c r="E154" t="n">
-        <v>2025000000</v>
-      </c>
-      <c r="F154" t="n">
-        <v>-1367644742.122094</v>
-      </c>
-      <c r="G154" t="n">
-        <v>-67.53801195664661</v>
-      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>page 14 (OCR table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5802,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BFXS5XCH7N0Y05NIXW11</t>
+          <t>R4DHLH5KX7NMDO6YTPM4</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5929,23 +5813,17 @@
       <c r="D155" t="n">
         <v>14694335353.459</v>
       </c>
-      <c r="E155" t="n">
-        <v>17600000</v>
-      </c>
-      <c r="F155" t="n">
-        <v>14676735353.459</v>
-      </c>
-      <c r="G155" t="n">
-        <v>83390.54178101705</v>
-      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>PDF non disponible</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>page 14 (OCR table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -6475,23 +6353,17 @@
       <c r="D169" t="n">
         <v>3097160515.81</v>
       </c>
-      <c r="E169" t="n">
-        <v>62000000</v>
-      </c>
-      <c r="F169" t="n">
-        <v>3035160515.81</v>
-      </c>
-      <c r="G169" t="n">
-        <v>4895.420186790322</v>
-      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
-          <t>ECART SIGNIFICATIF</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>page 142 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -7452,23 +7324,17 @@
       <c r="D198" t="n">
         <v>0.2453352409342637</v>
       </c>
-      <c r="E198" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0.0003352409342637086</v>
-      </c>
-      <c r="G198" t="n">
-        <v>0.1368330343933505</v>
-      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>page 108 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -7491,23 +7357,17 @@
       <c r="D199" t="n">
         <v>0.2453352409342637</v>
       </c>
-      <c r="E199" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0.0003352409342637086</v>
-      </c>
-      <c r="G199" t="n">
-        <v>0.1368330343933505</v>
-      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>page 108 (Qwen2.5-VL)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -7530,23 +7390,17 @@
       <c r="D200" t="n">
         <v>0.2470637829637899</v>
       </c>
-      <c r="E200" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="F200" t="n">
-        <v>6.378296378994897e-05</v>
-      </c>
-      <c r="G200" t="n">
-        <v>0.02582306226313723</v>
-      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>page 108 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -7570,22 +7424,22 @@
         <v>0.0965</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0965</v>
+        <v>0.113</v>
       </c>
       <c r="F201" t="n">
-        <v>0</v>
+        <v>-0.0165</v>
       </c>
       <c r="G201" t="n">
-        <v>0</v>
+        <v>-14.60176991150442</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>ECART SIGNIFICATIF</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>page 110</t>
+          <t>page 131 (table)</t>
         </is>
       </c>
     </row>
@@ -7609,13 +7463,13 @@
         <v>1.2087</v>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="F202" t="n">
-        <v>0.2087000000000001</v>
+        <v>-0.03129999999999988</v>
       </c>
       <c r="G202" t="n">
-        <v>20.87000000000001</v>
+        <v>-2.524193548387087</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -7624,7 +7478,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>page 54 (table)</t>
+          <t>page 130 (table)</t>
         </is>
       </c>
     </row>
@@ -7686,23 +7540,17 @@
       <c r="D204" t="n">
         <v>3868429342.22</v>
       </c>
-      <c r="E204" t="n">
-        <v>3869000000</v>
-      </c>
-      <c r="F204" t="n">
-        <v>-570657.7800002098</v>
-      </c>
-      <c r="G204" t="n">
-        <v>-0.01474949030757844</v>
-      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>page 108 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -7725,23 +7573,17 @@
       <c r="D205" t="n">
         <v>3868429342.22</v>
       </c>
-      <c r="E205" t="n">
-        <v>3869000000</v>
-      </c>
-      <c r="F205" t="n">
-        <v>-570657.7800002098</v>
-      </c>
-      <c r="G205" t="n">
-        <v>-0.01474949030757844</v>
-      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>page 108 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -7764,23 +7606,17 @@
       <c r="D206" t="n">
         <v>3895684875.02</v>
       </c>
-      <c r="E206" t="n">
-        <v>3896000000</v>
-      </c>
-      <c r="F206" t="n">
-        <v>-315124.9800000191</v>
-      </c>
-      <c r="G206" t="n">
-        <v>-0.008088423511294124</v>
-      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>page 108 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
@@ -7803,23 +7639,17 @@
       <c r="D207" t="n">
         <v>15767931779.75</v>
       </c>
-      <c r="E207" t="n">
-        <v>15768000000</v>
-      </c>
-      <c r="F207" t="n">
-        <v>-68220.25</v>
-      </c>
-      <c r="G207" t="n">
-        <v>-0.0004326499873160832</v>
-      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Non trouvé dans le PDF</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>page 108 (table)</t>
+          <t>auto-extraction (KM1/OV1 regex)</t>
         </is>
       </c>
     </row>
